--- a/data/nzd0403/nzd0403.xlsx
+++ b/data/nzd0403/nzd0403.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N277"/>
+  <dimension ref="A1:N278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13373,7 +13373,7 @@
         <v>381.21</v>
       </c>
       <c r="G276" t="n">
-        <v>402.52</v>
+        <v>397.2</v>
       </c>
       <c r="H276" t="n">
         <v>406.29</v>
@@ -13421,7 +13421,7 @@
         <v>382.47</v>
       </c>
       <c r="G277" t="n">
-        <v>404.1</v>
+        <v>400.16</v>
       </c>
       <c r="H277" t="n">
         <v>407.49</v>
@@ -13442,6 +13442,54 @@
         <v>436.47</v>
       </c>
       <c r="N277" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>309.92</v>
+      </c>
+      <c r="C278" t="n">
+        <v>332.93</v>
+      </c>
+      <c r="D278" t="n">
+        <v>345.7</v>
+      </c>
+      <c r="E278" t="n">
+        <v>369.13</v>
+      </c>
+      <c r="F278" t="n">
+        <v>386.78</v>
+      </c>
+      <c r="G278" t="n">
+        <v>397.3</v>
+      </c>
+      <c r="H278" t="n">
+        <v>404.51</v>
+      </c>
+      <c r="I278" t="n">
+        <v>407.5</v>
+      </c>
+      <c r="J278" t="n">
+        <v>328.59</v>
+      </c>
+      <c r="K278" t="n">
+        <v>333.82</v>
+      </c>
+      <c r="L278" t="n">
+        <v>338.66</v>
+      </c>
+      <c r="M278" t="n">
+        <v>438.34</v>
+      </c>
+      <c r="N278" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -13458,7 +13506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B292"/>
+  <dimension ref="A1:B293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16381,6 +16429,16 @@
       </c>
       <c r="B292" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>
@@ -16549,28 +16607,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.431152719312647</v>
+        <v>-1.415553623161103</v>
       </c>
       <c r="J2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K2" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1873760279686338</v>
+        <v>0.184924830495417</v>
       </c>
       <c r="M2" t="n">
-        <v>18.51165870823181</v>
+        <v>18.50286644366998</v>
       </c>
       <c r="N2" t="n">
-        <v>478.3147026397535</v>
+        <v>477.9572371869816</v>
       </c>
       <c r="O2" t="n">
-        <v>21.8704070067238</v>
+        <v>21.86223312443131</v>
       </c>
       <c r="P2" t="n">
-        <v>328.9666941453552</v>
+        <v>328.793002296135</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -16631,28 +16689,28 @@
         <v>0.08690000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.360377904285458</v>
+        <v>-1.333179223339582</v>
       </c>
       <c r="J3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1940624662153037</v>
+        <v>0.1873347582010819</v>
       </c>
       <c r="M3" t="n">
-        <v>17.37179931842651</v>
+        <v>17.43391667942047</v>
       </c>
       <c r="N3" t="n">
-        <v>422.2291119463432</v>
+        <v>425.4974433056497</v>
       </c>
       <c r="O3" t="n">
-        <v>20.54821432500506</v>
+        <v>20.62758937214064</v>
       </c>
       <c r="P3" t="n">
-        <v>333.8430237098719</v>
+        <v>333.5401433919928</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16713,28 +16771,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.671944039285909</v>
+        <v>-1.635076190606918</v>
       </c>
       <c r="J4" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1860037443457966</v>
+        <v>0.1785697553173187</v>
       </c>
       <c r="M4" t="n">
-        <v>20.47623546732988</v>
+        <v>20.5981131141371</v>
       </c>
       <c r="N4" t="n">
-        <v>641.5730050929119</v>
+        <v>647.8265160723662</v>
       </c>
       <c r="O4" t="n">
-        <v>25.32929144474657</v>
+        <v>25.45243634845918</v>
       </c>
       <c r="P4" t="n">
-        <v>342.8655286968826</v>
+        <v>342.4407138751704</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16795,28 +16853,28 @@
         <v>0.06950000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7834286387750213</v>
+        <v>-0.7490802036261099</v>
       </c>
       <c r="J5" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K5" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0554664208918243</v>
+        <v>0.05069239362342604</v>
       </c>
       <c r="M5" t="n">
-        <v>18.65246908391653</v>
+        <v>18.70812560172834</v>
       </c>
       <c r="N5" t="n">
-        <v>524.7333527399766</v>
+        <v>529.8169406477181</v>
       </c>
       <c r="O5" t="n">
-        <v>22.90705901550822</v>
+        <v>23.01775272800796</v>
       </c>
       <c r="P5" t="n">
-        <v>347.6796733876863</v>
+        <v>347.2681059378167</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16877,28 +16935,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7087551450264655</v>
+        <v>0.7463894427072874</v>
       </c>
       <c r="J6" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01369212813321841</v>
+        <v>0.01521596754184562</v>
       </c>
       <c r="M6" t="n">
-        <v>27.58718153151973</v>
+        <v>27.6429263898076</v>
       </c>
       <c r="N6" t="n">
-        <v>1858.107009103747</v>
+        <v>1859.820903298188</v>
       </c>
       <c r="O6" t="n">
-        <v>43.10576538125436</v>
+        <v>43.12564090304268</v>
       </c>
       <c r="P6" t="n">
-        <v>319.2033005425346</v>
+        <v>318.7648280373148</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16959,28 +17017,28 @@
         <v>0.0355</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6912946732518245</v>
+        <v>-0.6444126651108198</v>
       </c>
       <c r="J7" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K7" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02246238308563908</v>
+        <v>0.01949914794852647</v>
       </c>
       <c r="M7" t="n">
-        <v>24.52655646023107</v>
+        <v>24.66482711187029</v>
       </c>
       <c r="N7" t="n">
-        <v>1124.67101127237</v>
+        <v>1134.217020940518</v>
       </c>
       <c r="O7" t="n">
-        <v>33.53611502950766</v>
+        <v>33.67813862048374</v>
       </c>
       <c r="P7" t="n">
-        <v>344.8448102061963</v>
+        <v>344.3146786397351</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -17041,28 +17099,28 @@
         <v>0.0548</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7868789771736295</v>
+        <v>0.8391367184661582</v>
       </c>
       <c r="J8" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K8" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0188988668908121</v>
+        <v>0.02139217390484027</v>
       </c>
       <c r="M8" t="n">
-        <v>31.03740823107842</v>
+        <v>31.14645764607312</v>
       </c>
       <c r="N8" t="n">
-        <v>1690.480184590092</v>
+        <v>1701.746063929071</v>
       </c>
       <c r="O8" t="n">
-        <v>41.11544946355435</v>
+        <v>41.25222495731681</v>
       </c>
       <c r="P8" t="n">
-        <v>313.8907299134661</v>
+        <v>313.2936882680594</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -17123,28 +17181,28 @@
         <v>0.0543</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4228793637003715</v>
+        <v>-0.3535469333053943</v>
       </c>
       <c r="J9" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005695169189623872</v>
+        <v>0.003947272596785734</v>
       </c>
       <c r="M9" t="n">
-        <v>31.54753672513792</v>
+        <v>31.75908160528159</v>
       </c>
       <c r="N9" t="n">
-        <v>1654.917831792327</v>
+        <v>1679.467666827146</v>
       </c>
       <c r="O9" t="n">
-        <v>40.68068130934298</v>
+        <v>40.98130874956467</v>
       </c>
       <c r="P9" t="n">
-        <v>327.9499654211758</v>
+        <v>327.1601704765627</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -17205,28 +17263,28 @@
         <v>0.0586</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8663343282460563</v>
+        <v>-0.8481838747355095</v>
       </c>
       <c r="J10" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K10" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02136628414878883</v>
+        <v>0.02064588475653129</v>
       </c>
       <c r="M10" t="n">
-        <v>34.29716807949939</v>
+        <v>34.26743942019711</v>
       </c>
       <c r="N10" t="n">
-        <v>1845.662132686027</v>
+        <v>1840.791232790578</v>
       </c>
       <c r="O10" t="n">
-        <v>42.96117005722758</v>
+        <v>42.90444304254022</v>
       </c>
       <c r="P10" t="n">
-        <v>328.377644349931</v>
+        <v>328.1736120655469</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -17287,28 +17345,28 @@
         <v>0.0709</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.657928173593657</v>
+        <v>-0.6477963422707435</v>
       </c>
       <c r="J11" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K11" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02019152469467012</v>
+        <v>0.01973625701717707</v>
       </c>
       <c r="M11" t="n">
-        <v>24.39963701091695</v>
+        <v>24.36230674834477</v>
       </c>
       <c r="N11" t="n">
-        <v>1117.805980211043</v>
+        <v>1114.289113218265</v>
       </c>
       <c r="O11" t="n">
-        <v>33.43360555206457</v>
+        <v>33.38096932712208</v>
       </c>
       <c r="P11" t="n">
-        <v>338.3386481825936</v>
+        <v>338.2240392941339</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -17369,28 +17427,28 @@
         <v>0.1599</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5339831320276144</v>
+        <v>-0.524242988456937</v>
       </c>
       <c r="J12" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K12" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01372154215955346</v>
+        <v>0.01333716307828625</v>
       </c>
       <c r="M12" t="n">
-        <v>23.10384673564395</v>
+        <v>23.0718893642976</v>
       </c>
       <c r="N12" t="n">
-        <v>1098.62973014966</v>
+        <v>1095.078444190763</v>
       </c>
       <c r="O12" t="n">
-        <v>33.14558387100249</v>
+        <v>33.09196948189641</v>
       </c>
       <c r="P12" t="n">
-        <v>340.5101828040586</v>
+        <v>340.4009498367541</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -17451,28 +17509,28 @@
         <v>0.0668</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.005202357304422</v>
+        <v>-0.9220425766419533</v>
       </c>
       <c r="J13" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K13" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L13" t="n">
-        <v>0.07441037920538551</v>
+        <v>0.06005933519015205</v>
       </c>
       <c r="M13" t="n">
-        <v>20.11019904935186</v>
+        <v>20.47278377324295</v>
       </c>
       <c r="N13" t="n">
-        <v>667.2679995513674</v>
+        <v>709.5692968103476</v>
       </c>
       <c r="O13" t="n">
-        <v>25.83153111124789</v>
+        <v>26.63774196155424</v>
       </c>
       <c r="P13" t="n">
-        <v>354.6105316443708</v>
+        <v>353.6674743304961</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -17514,7 +17572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N277"/>
+  <dimension ref="A1:N278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36742,7 +36800,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>-42.77960683892681,173.3746885564902</t>
+          <t>-42.77958832372822,173.37462857307943</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -36814,7 +36872,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>-42.77961233779549,173.37470637111906</t>
+          <t>-42.77959862542157,173.3746619473036</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -36848,6 +36906,78 @@
         </is>
       </c>
       <c r="N277" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:31+00:00</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>-42.77636940049545,173.37587108409772</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>-42.77703798729965,173.37563527417274</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>-42.77765807819068,173.37529299396337</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-42.77832033510764,173.37506779853345</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-42.77896448971036,173.37487088732354</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-42.77958867175857,173.37462970058684</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-42.780201020893706,173.37439230820823</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-42.780820937914605,173.3741506558442</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-42.78122639768312,173.37295057353256</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-42.78187466986038,173.3727399688572</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-42.782532209271906,173.37259615482634</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-42.783358831457896,173.37360564571176</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
